--- a/起源小说平台接口测试用例.xlsx
+++ b/起源小说平台接口测试用例.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="142">
   <si>
     <t>编号</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -156,6 +162,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "login",
         "http_method": "GET",
@@ -198,6 +210,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -282,6 +300,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -360,6 +384,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -420,6 +450,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -480,6 +516,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">   {
         "name": "register",
         "http_method": "GET",
@@ -519,6 +561,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -588,6 +636,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -649,6 +703,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">  {
         "name": "listBookCategory",
         "http_method": "GET",
@@ -747,6 +807,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -905,6 +971,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -953,6 +1025,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1001,6 +1079,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1049,6 +1133,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1118,6 +1208,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1141,6 +1237,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "listNewRank",
         "http_method": "GET",
@@ -1209,6 +1311,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1238,6 +1346,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1270,6 +1384,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1292,6 +1412,39 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>{
+        "name": "listBookCategory",
+        "http_method": "GET",
+        "path": "/book/listBookCategory",
+        "return_type": "RestResult&lt;List&lt;BookCategory&gt;&gt;",
+        "response_type": "List&lt;BookCategory",
+        "description": "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>查询小说分类列表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>",
+        "parameters": [],
+        "controller_class": "BookController",
+        "raw_signature": "RestResult&lt;List&lt;BookCategory&gt;&gt; listBookCategory()"
+      }</t>
+    </r>
+  </si>
+  <si>
     <t>YDSG_API_01</t>
   </si>
   <si>
@@ -1302,6 +1455,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1381,6 +1540,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> {
         "name": "addToBookShelf",
         "http_method": "POST",
@@ -1448,6 +1613,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1508,6 +1679,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "queryIsInShelf",
         "http_method": "GET",
@@ -1566,6 +1743,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1626,6 +1809,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "listBookShelfByPage",
         "http_method": "GET",
@@ -1696,6 +1885,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1756,6 +1951,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "queryBookDetail",
         "http_method": "GET",
@@ -1808,6 +2009,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1859,6 +2066,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "addReadHistory",
         "http_method": "POST",
@@ -1926,6 +2139,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1959,6 +2178,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "listReadHistoryByPage",
         "http_method": "GET",
@@ -2029,6 +2254,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2116,6 +2347,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "commentReplyList",
         "http_method": "GET",
@@ -2174,6 +2411,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2243,6 +2486,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "listCommentByPage",
         "http_method": "GET",
@@ -2310,6 +2559,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2352,6 +2607,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> {
         "name": "toggleCommentLike",
         "http_method": "POST",
@@ -2431,6 +2692,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2500,6 +2767,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> {
         "name": "queryIsInShelf",
         "http_method": "GET",
@@ -2561,6 +2834,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2658,6 +2937,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> {
         "name": "addBook",
         "http_method": "POST",
@@ -2728,6 +3013,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2834,6 +3125,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "addBookContent",
         "http_method": "POST",
@@ -2919,6 +3216,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2988,6 +3291,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> {
         "name": "updateBookPic",
         "http_method": "POST",
@@ -3055,6 +3364,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -3142,6 +3457,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "updateBookContent",
         "http_method": "POST",
@@ -3218,6 +3539,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -3269,6 +3596,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "deleteIndex",
         "http_method": "DELETE",
@@ -3330,6 +3663,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -3381,6 +3720,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>{
         "name": "listBookByPage",
         "http_method": "GET",
@@ -3451,6 +3796,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -4806,7 +5157,7 @@
         <v>64</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>18</v>
@@ -4814,19 +5165,19 @@
     </row>
     <row r="18" ht="71.1" customHeight="1" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -4834,19 +5185,19 @@
     </row>
     <row r="19" ht="71.1" customHeight="1" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -4854,19 +5205,19 @@
     </row>
     <row r="20" ht="71.1" customHeight="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -4874,19 +5225,19 @@
     </row>
     <row r="21" ht="71.1" customHeight="1" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -4894,19 +5245,19 @@
     </row>
     <row r="22" ht="71.1" customHeight="1" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>18</v>
@@ -4914,19 +5265,19 @@
     </row>
     <row r="23" ht="71.1" customHeight="1" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>18</v>
@@ -4934,19 +5285,19 @@
     </row>
     <row r="24" ht="71.1" customHeight="1" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>18</v>
@@ -4954,19 +5305,19 @@
     </row>
     <row r="25" ht="71.1" customHeight="1" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>18</v>
@@ -4974,19 +5325,19 @@
     </row>
     <row r="26" ht="71.1" customHeight="1" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>18</v>
@@ -4994,19 +5345,19 @@
     </row>
     <row r="27" ht="57.3" customHeight="1" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -5014,19 +5365,19 @@
     </row>
     <row r="28" ht="57.3" customHeight="1" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -5034,19 +5385,19 @@
     </row>
     <row r="29" ht="71.1" customHeight="1" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -5054,19 +5405,19 @@
     </row>
     <row r="30" ht="71.1" customHeight="1" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>18</v>
@@ -5074,19 +5425,19 @@
     </row>
     <row r="31" ht="71.1" customHeight="1" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>18</v>
@@ -5094,19 +5445,19 @@
     </row>
     <row r="32" ht="71.1" customHeight="1" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>18</v>
@@ -5114,19 +5465,19 @@
     </row>
     <row r="33" ht="59.1" customHeight="1" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -5134,19 +5485,19 @@
     </row>
     <row r="34" ht="71.1" customHeight="1" spans="1:6">
       <c r="A34" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>18</v>
